--- a/practice/answers/s1_q01.xlsx
+++ b/practice/answers/s1_q01.xlsx
@@ -501,7 +501,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Q1 — Revenue per acre with a locked price</t>
+          <t>Revenue per acre with a locked price</t>
         </is>
       </c>
     </row>

--- a/practice/answers/s1_q01.xlsx
+++ b/practice/answers/s1_q01.xlsx
@@ -554,14 +554,14 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Willow</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>41.2</v>
+        <v>52.4</v>
       </c>
       <c r="D7" s="10">
         <f>C7*$B$4</f>
@@ -575,14 +575,14 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>240</v>
+        <v>147</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>38.6</v>
+        <v>61.8</v>
       </c>
       <c r="D8" s="10">
         <f>C8*$B$4</f>
@@ -596,14 +596,14 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Creek</t>
+          <t>Slough</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>44.8</v>
+        <v>47.9</v>
       </c>
       <c r="D9" s="10">
         <f>C9*$B$4</f>
@@ -617,14 +617,14 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Quarter</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>310</v>
+        <v>89</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>36.1</v>
+        <v>64.5</v>
       </c>
       <c r="D10" s="10">
         <f>C10*$B$4</f>
@@ -638,14 +638,14 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Rented</t>
+          <t>Airport</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>175</v>
+        <v>255</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>39.9</v>
+        <v>55.2</v>
       </c>
       <c r="D11" s="10">
         <f>C11*$B$4</f>

--- a/practice/answers/s1_q01.xlsx
+++ b/practice/answers/s1_q01.xlsx
@@ -1,87 +1,150 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59976752FD9CD15DFD5FD05676C0F2775DE2FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{459A3E13-169A-4B2F-AEAF-D586A1A23F0E}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Answer" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>Revenue per acre with a locked price</t>
+  </si>
+  <si>
+    <t>The canola price sits in one cell. Each row multiplies its own yield by that one cell, so the reference to the price must be absolute. Column E shows what was typed into column D.</t>
+  </si>
+  <si>
+    <t>Canola price ($/bu)</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Acres</t>
+  </si>
+  <si>
+    <t>Yield (bu/ac)</t>
+  </si>
+  <si>
+    <t>Revenue ($/ac)</t>
+  </si>
+  <si>
+    <t>The formula in D</t>
+  </si>
+  <si>
+    <t>Willow</t>
+  </si>
+  <si>
+    <t>Ridge</t>
+  </si>
+  <si>
+    <t>Slough</t>
+  </si>
+  <si>
+    <t>Quarter</t>
+  </si>
+  <si>
+    <t>Airport</t>
+  </si>
+  <si>
+    <t>With =C7*B4 instead, filling down walks the price to B5, B6, B7 -- empty cells -- so every revenue below the first comes out as $0.00.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="8">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF4A7C59"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF5C6B62"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF24302A"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF24302A"/>
       <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF2F5D46"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5C6B62"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="FFF6EFD9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="FF4A7C59"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,105 +160,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -483,188 +488,164 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Revenue per acre with a locked price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>The canola price sits in one cell. Each row multiplies its own yield by that one cell, so the reference to the price must be absolute. Column E shows what was typed into column D.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Canola price ($/bu)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
+    <row r="1" spans="1:6" ht="18" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="32.1" customHeight="1">
+      <c r="A2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+    </row>
+    <row r="3" spans="1:6" ht="18" customHeight="1"/>
+    <row r="4" spans="1:6" ht="18" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
         <v>14.2</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1"/>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Acres</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Yield (bu/ac)</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Revenue ($/ac)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>The formula in D</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Willow</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
+    <row r="5" spans="1:6" ht="18" customHeight="1"/>
+    <row r="6" spans="1:6" ht="18" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18" customHeight="1">
+      <c r="A7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="7">
         <v>213</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8">
         <v>52.4</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <f>C7*$B$4</f>
-        <v/>
-      </c>
-      <c r="E7" s="11">
-        <f>_xlfn.FORMULATEXT(D7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
+        <v>744.07999999999993</v>
+      </c>
+      <c r="E7" s="10" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(D7)</f>
+        <v>=C7*$B$4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="18" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="7">
         <v>147</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8">
         <v>61.8</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <f>C8*$B$4</f>
-        <v/>
-      </c>
-      <c r="E8" s="11">
-        <f>_xlfn.FORMULATEXT(D8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Slough</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
+        <v>877.56</v>
+      </c>
+      <c r="E8" s="10" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(D8)</f>
+        <v>=C8*$B$4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="7">
         <v>326</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8">
         <v>47.9</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <f>C9*$B$4</f>
-        <v/>
-      </c>
-      <c r="E9" s="11">
-        <f>_xlfn.FORMULATEXT(D9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Quarter</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
+        <v>680.18</v>
+      </c>
+      <c r="E9" s="10" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(D9)</f>
+        <v>=C9*$B$4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18" customHeight="1">
+      <c r="A10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="7">
         <v>89</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="8">
         <v>64.5</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <f>C10*$B$4</f>
-        <v/>
-      </c>
-      <c r="E10" s="11">
-        <f>_xlfn.FORMULATEXT(D10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Airport</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
+        <v>915.9</v>
+      </c>
+      <c r="E10" s="10" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(D10)</f>
+        <v>=C10*$B$4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="18" customHeight="1">
+      <c r="A11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="7">
         <v>255</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="8">
         <v>55.2</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <f>C11*$B$4</f>
-        <v/>
-      </c>
-      <c r="E11" s="11">
-        <f>_xlfn.FORMULATEXT(D11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1"/>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>With =C7*B4 instead, filling down walks the price to B5, B6, B7 -- empty cells -- so every revenue below the first comes out as $0.00.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1"/>
+        <v>783.84</v>
+      </c>
+      <c r="E11" s="10" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(D11)</f>
+        <v>=C11*$B$4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18" customHeight="1"/>
+    <row r="13" spans="1:6" ht="30" customHeight="1">
+      <c r="A13" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+    </row>
+    <row r="14" spans="1:6" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>

--- a/practice/answers/s1_q01.xlsx
+++ b/practice/answers/s1_q01.xlsx
@@ -1,150 +1,68 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59976752FD9CD15DFD5FD05676C0F2775DE2FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{459A3E13-169A-4B2F-AEAF-D586A1A23F0E}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>Revenue per acre with a locked price</t>
-  </si>
-  <si>
-    <t>The canola price sits in one cell. Each row multiplies its own yield by that one cell, so the reference to the price must be absolute. Column E shows what was typed into column D.</t>
-  </si>
-  <si>
-    <t>Canola price ($/bu)</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Acres</t>
-  </si>
-  <si>
-    <t>Yield (bu/ac)</t>
-  </si>
-  <si>
-    <t>Revenue ($/ac)</t>
-  </si>
-  <si>
-    <t>The formula in D</t>
-  </si>
-  <si>
-    <t>Willow</t>
-  </si>
-  <si>
-    <t>Ridge</t>
-  </si>
-  <si>
-    <t>Slough</t>
-  </si>
-  <si>
-    <t>Quarter</t>
-  </si>
-  <si>
-    <t>Airport</t>
-  </si>
-  <si>
-    <t>With =C7*B4 instead, filling down walks the price to B5, B6, B7 -- empty cells -- so every revenue below the first comes out as $0.00.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FF4A7C59"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF5C6B62"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF24302A"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF24302A"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF2F5D46"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF5C6B62"/>
-      <name val="Arial"/>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6EFD9"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4A7C59"/>
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -160,47 +78,107 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+  <cellXfs count="25">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -488,168 +466,270 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="32.1" customHeight="1">
-      <c r="A2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-    </row>
-    <row r="3" spans="1:6" ht="18" customHeight="1"/>
-    <row r="4" spans="1:6" ht="18" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Acres</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Yield (bu/ac)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Revenue ($/ac)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total revenue ($)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Canola price ($/bu)</t>
+        </is>
+      </c>
+      <c r="G1" s="20" t="n">
         <v>14.2</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="18" customHeight="1"/>
-    <row r="6" spans="1:6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="18" customHeight="1">
-      <c r="A7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="7">
-        <v>213</v>
-      </c>
-      <c r="C7" s="8">
-        <v>52.4</v>
-      </c>
-      <c r="D7" s="9">
-        <f>C7*$B$4</f>
-        <v>744.07999999999993</v>
-      </c>
-      <c r="E7" s="10" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(D7)</f>
-        <v>=C7*$B$4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="18" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7">
-        <v>147</v>
-      </c>
-      <c r="C8" s="8">
-        <v>61.8</v>
-      </c>
-      <c r="D8" s="9">
-        <f>C8*$B$4</f>
-        <v>877.56</v>
-      </c>
-      <c r="E8" s="10" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(D8)</f>
-        <v>=C8*$B$4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="7">
-        <v>326</v>
-      </c>
-      <c r="C9" s="8">
-        <v>47.9</v>
-      </c>
-      <c r="D9" s="9">
-        <f>C9*$B$4</f>
-        <v>680.18</v>
-      </c>
-      <c r="E9" s="10" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(D9)</f>
-        <v>=C9*$B$4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1">
-      <c r="A10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="7">
-        <v>89</v>
-      </c>
-      <c r="C10" s="8">
-        <v>64.5</v>
-      </c>
-      <c r="D10" s="9">
-        <f>C10*$B$4</f>
-        <v>915.9</v>
-      </c>
-      <c r="E10" s="10" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(D10)</f>
-        <v>=C10*$B$4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="18" customHeight="1">
-      <c r="A11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="7">
-        <v>255</v>
-      </c>
-      <c r="C11" s="8">
-        <v>55.2</v>
-      </c>
-      <c r="D11" s="9">
-        <f>C11*$B$4</f>
-        <v>783.84</v>
-      </c>
-      <c r="E11" s="10" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(D11)</f>
-        <v>=C11*$B$4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1"/>
-    <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1"/>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Incorrect (no $ signs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Kestrel</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="C2" s="21" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="D2" s="22">
+        <f>C2*$G$1</f>
+        <v/>
+      </c>
+      <c r="E2" s="9">
+        <f>D2*B2</f>
+        <v/>
+      </c>
+      <c r="H2" s="23">
+        <f>C2*G1</f>
+        <v/>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>Only the first row is right; the rows below show $0.00 because the unanchored price reference walks down to G2, G3, ... which are empty and treated as zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Meadowvale</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="C3" s="21" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="D3" s="22">
+        <f>C3*$G$1</f>
+        <v/>
+      </c>
+      <c r="E3" s="9">
+        <f>D3*B3</f>
+        <v/>
+      </c>
+      <c r="H3" s="23">
+        <f>C3*G2</f>
+        <v/>
+      </c>
+      <c r="I3" s="19" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nightjar</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="C4" s="21" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="D4" s="22">
+        <f>C4*$G$1</f>
+        <v/>
+      </c>
+      <c r="E4" s="9">
+        <f>D4*B4</f>
+        <v/>
+      </c>
+      <c r="H4" s="23">
+        <f>C4*G3</f>
+        <v/>
+      </c>
+      <c r="I4" s="19" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>310</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="D5" s="22">
+        <f>C5*$G$1</f>
+        <v/>
+      </c>
+      <c r="E5" s="9">
+        <f>D5*B5</f>
+        <v/>
+      </c>
+      <c r="H5" s="23">
+        <f>C5*G4</f>
+        <v/>
+      </c>
+      <c r="I5" s="19" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rented</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="D6" s="22">
+        <f>C6*$G$1</f>
+        <v/>
+      </c>
+      <c r="E6" s="9">
+        <f>D6*B6</f>
+        <v/>
+      </c>
+      <c r="H6" s="23">
+        <f>C6*G5</f>
+        <v/>
+      </c>
+      <c r="I6" s="19" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Total acres</t>
+        </is>
+      </c>
+      <c r="B8" s="13">
+        <f>SUM(B2:B6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Total bushels</t>
+        </is>
+      </c>
+      <c r="B9" s="14">
+        <f>SUMPRODUCT(B2:B6,C2:C6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Total revenue ($)</t>
+        </is>
+      </c>
+      <c r="B10" s="24">
+        <f>SUM(E2:E6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:E13"/>
+  <mergeCells count="1">
+    <mergeCell ref="I2:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q01.xlsx
+++ b/practice/answers/s1_q01.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -33,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -60,11 +59,6 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -78,34 +72,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -471,18 +452,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,27 +480,24 @@
           <t>Yield (bu/ac)</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Revenue ($/ac)</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Total revenue ($)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Bushels</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Canola price ($/bu)</t>
-        </is>
-      </c>
-      <c r="G1" s="20" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>Incorrect (no $ signs)</t>
         </is>
       </c>
     </row>
@@ -531,28 +507,26 @@
           <t>Kestrel</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" t="n">
         <v>120</v>
       </c>
-      <c r="C2" s="21" t="n">
+      <c r="C2" t="n">
         <v>41.2</v>
       </c>
-      <c r="D2" s="22">
-        <f>C2*$G$1</f>
-        <v/>
-      </c>
-      <c r="E2" s="9">
+      <c r="D2" s="2">
+        <f>C2*$H$2</f>
+        <v/>
+      </c>
+      <c r="E2" s="3">
         <f>D2*B2</f>
         <v/>
       </c>
-      <c r="H2" s="23">
-        <f>C2*G1</f>
-        <v/>
-      </c>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>Only the first row is right; the rows below show $0.00 because the unanchored price reference walks down to G2, G3, ... which are empty and treated as zero.</t>
-        </is>
+      <c r="F2" s="4">
+        <f>B2*C2</f>
+        <v/>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>14.2</v>
       </c>
     </row>
     <row r="3">
@@ -561,25 +535,24 @@
           <t>Meadowvale</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" t="n">
         <v>240</v>
       </c>
-      <c r="C3" s="21" t="n">
+      <c r="C3" t="n">
         <v>38.6</v>
       </c>
-      <c r="D3" s="22">
-        <f>C3*$G$1</f>
-        <v/>
-      </c>
-      <c r="E3" s="9">
+      <c r="D3" s="2">
+        <f>C3*$H$2</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
         <f>D3*B3</f>
         <v/>
       </c>
-      <c r="H3" s="23">
-        <f>C3*G2</f>
-        <v/>
-      </c>
-      <c r="I3" s="19" t="n"/>
+      <c r="F3" s="4">
+        <f>B3*C3</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -587,25 +560,24 @@
           <t>Nightjar</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" t="n">
         <v>95</v>
       </c>
-      <c r="C4" s="21" t="n">
+      <c r="C4" t="n">
         <v>44.8</v>
       </c>
-      <c r="D4" s="22">
-        <f>C4*$G$1</f>
-        <v/>
-      </c>
-      <c r="E4" s="9">
+      <c r="D4" s="2">
+        <f>C4*$H$2</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
         <f>D4*B4</f>
         <v/>
       </c>
-      <c r="H4" s="23">
-        <f>C4*G3</f>
-        <v/>
-      </c>
-      <c r="I4" s="19" t="n"/>
+      <c r="F4" s="4">
+        <f>B4*C4</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -613,25 +585,24 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" t="n">
         <v>310</v>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" t="n">
         <v>36.1</v>
       </c>
-      <c r="D5" s="22">
-        <f>C5*$G$1</f>
-        <v/>
-      </c>
-      <c r="E5" s="9">
+      <c r="D5" s="2">
+        <f>C5*$H$2</f>
+        <v/>
+      </c>
+      <c r="E5" s="3">
         <f>D5*B5</f>
         <v/>
       </c>
-      <c r="H5" s="23">
-        <f>C5*G4</f>
-        <v/>
-      </c>
-      <c r="I5" s="19" t="n"/>
+      <c r="F5" s="4">
+        <f>B5*C5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -639,97 +610,89 @@
           <t>Rented</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" t="n">
         <v>175</v>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C6" t="n">
         <v>39.9</v>
       </c>
-      <c r="D6" s="22">
-        <f>C6*$G$1</f>
-        <v/>
-      </c>
-      <c r="E6" s="9">
+      <c r="D6" s="2">
+        <f>C6*$H$2</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
         <f>D6*B6</f>
         <v/>
       </c>
-      <c r="H6" s="23">
-        <f>C6*G5</f>
-        <v/>
-      </c>
-      <c r="I6" s="19" t="n"/>
+      <c r="F6" s="4">
+        <f>B6*C6</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Total acres</t>
-        </is>
-      </c>
-      <c r="B8" s="13">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Totals (c)</t>
+        </is>
+      </c>
+      <c r="B8" s="4">
         <f>SUM(B2:B6)</f>
         <v/>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Total bushels</t>
-        </is>
-      </c>
-      <c r="B9" s="14">
-        <f>SUMPRODUCT(B2:B6,C2:C6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Total revenue ($)</t>
-        </is>
-      </c>
-      <c r="B10" s="24">
+      <c r="E8" s="6">
         <f>SUM(E2:E6)</f>
         <v/>
       </c>
+      <c r="F8" s="4">
+        <f>SUM(F2:F6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>(d) The price sits in one cell (H2), so as the part a formula fills down every copy must keep pointing at it -- the $ signs lock that reference. In part b, revenue per acre and acres both sit on the same row as the formula, so both references should shift down together and no $ is needed.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Legend: colours mark question parts</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Part (a)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Part (b)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Part (c)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Part (d)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>Part (e)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="I2:I6"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q01.xlsx
+++ b/practice/answers/s1_q01.xlsx
@@ -648,7 +648,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="64" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>(d) The price sits in one cell (H2), so as the part a formula fills down every copy must keep pointing at it -- the $ signs lock that reference. In part b, revenue per acre and acres both sit on the same row as the formula, so both references should shift down together and no $ is needed.</t>
